--- a/output/yearly_benthic_cover_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_98_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32771534845229</v>
+        <v>45.64127654286858</v>
       </c>
       <c r="M2" t="n">
-        <v>99.58632742872862</v>
+        <v>99.03310677052588</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99216684076964</v>
+        <v>88.04731160931718</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92396932087679</v>
+        <v>45.95694574902397</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228644011836538</v>
+        <v>2.228760485392507</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701685012017402</v>
+        <v>5.72350551327634</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428813372788459</v>
+        <v>0.7429201617975025</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97186431667427</v>
+        <v>33.98274080401357</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17254151482691</v>
+        <v>34.17432744268511</v>
       </c>
       <c r="I3" t="n">
-        <v>6.531542290142886</v>
+        <v>6.55180619091776</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643008357992787</v>
+        <v>4.643251011234391</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00783315923037</v>
+        <v>11.95268839068282</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83373953538017</v>
+        <v>48.85519276802567</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655420154873</v>
+        <v>106.7648269077325</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05052966482978</v>
+        <v>87.08078589422487</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61059615327594</v>
+        <v>42.62137433145953</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183111400179261</v>
+        <v>2.181951778964969</v>
       </c>
       <c r="E4" t="n">
-        <v>6.494249279359097</v>
+        <v>6.515178599389378</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444328930060397</v>
+        <v>0.7444760806760586</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27779756712187</v>
+        <v>33.26903103200185</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24391307827783</v>
+        <v>34.24589971109869</v>
       </c>
       <c r="I4" t="n">
-        <v>5.454319865597935</v>
+        <v>5.471273187868574</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652705581287748</v>
+        <v>4.652975504225366</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94947033517022</v>
+        <v>12.91921410577512</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2585017812721</v>
+        <v>44.27741694635097</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81856826971826</v>
+        <v>99.81800538358561</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.83721708275147</v>
+        <v>85.80722986251979</v>
       </c>
       <c r="C5" t="n">
-        <v>42.24382298336545</v>
+        <v>42.19698051319777</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123725940054304</v>
+        <v>2.119489615681723</v>
       </c>
       <c r="E5" t="n">
-        <v>7.076475241380629</v>
+        <v>7.089917642335306</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457491941730012</v>
+        <v>0.7457970193668998</v>
       </c>
       <c r="G5" t="n">
-        <v>32.37256784760027</v>
+        <v>32.3166471761212</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30446293195806</v>
+        <v>34.30666289087738</v>
       </c>
       <c r="I5" t="n">
-        <v>4.553303464003942</v>
+        <v>4.567484147094148</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660932463581258</v>
+        <v>4.661231371043123</v>
       </c>
       <c r="K5" t="n">
-        <v>14.16278291724853</v>
+        <v>14.19277013748023</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44188521423052</v>
+        <v>43.45826953854787</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84849111484451</v>
+        <v>99.84802018922586</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.30952441560115</v>
+        <v>84.33034745541606</v>
       </c>
       <c r="C6" t="n">
-        <v>41.42322881494731</v>
+        <v>41.42934184460893</v>
       </c>
       <c r="D6" t="n">
-        <v>2.048757991765224</v>
+        <v>2.047189530600626</v>
       </c>
       <c r="E6" t="n">
-        <v>7.46002766914196</v>
+        <v>7.483394833479589</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468696436118035</v>
+        <v>0.7469207576779221</v>
       </c>
       <c r="G6" t="n">
-        <v>31.22980976068744</v>
+        <v>31.21426086430252</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35600360614296</v>
+        <v>34.35835485318441</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80012047167798</v>
+        <v>3.811971880683982</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667935272573772</v>
+        <v>4.668254735487013</v>
       </c>
       <c r="K6" t="n">
-        <v>15.69047558439887</v>
+        <v>15.66965254458394</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75981494887593</v>
+        <v>42.77413105116563</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8735193482221</v>
+        <v>99.87312544035851</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.71430778945546</v>
+        <v>82.63995388027118</v>
       </c>
       <c r="C7" t="n">
-        <v>40.41804294901602</v>
+        <v>40.33081294989967</v>
       </c>
       <c r="D7" t="n">
-        <v>1.971049425457283</v>
+        <v>1.964774668788305</v>
       </c>
       <c r="E7" t="n">
-        <v>7.70554075619798</v>
+        <v>7.712251384697774</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478240066855926</v>
+        <v>0.7478790289682603</v>
       </c>
       <c r="G7" t="n">
-        <v>30.04527564180803</v>
+        <v>29.95765078631405</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39990430753726</v>
+        <v>34.40243533253997</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170813609984361</v>
+        <v>3.180718747911204</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673900041784954</v>
+        <v>4.674243931051627</v>
       </c>
       <c r="K7" t="n">
-        <v>17.28569221054456</v>
+        <v>17.36004611972881</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19070593844838</v>
+        <v>42.20325282257474</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89444109800895</v>
+        <v>99.89411189220323</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.66228536753937</v>
+        <v>87.56508020857744</v>
       </c>
       <c r="C8" t="n">
-        <v>42.70734353194172</v>
+        <v>42.5997801255621</v>
       </c>
       <c r="D8" t="n">
-        <v>1.975324318569502</v>
+        <v>1.969046133648937</v>
       </c>
       <c r="E8" t="n">
-        <v>9.534133348657097</v>
+        <v>9.527661826504991</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494459181678936</v>
+        <v>0.7495049350036899</v>
       </c>
       <c r="G8" t="n">
-        <v>30.54106539081457</v>
+        <v>30.44618012223764</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4745122357231</v>
+        <v>34.47722701016972</v>
       </c>
       <c r="I8" t="n">
-        <v>5.703767167057864</v>
+        <v>5.711054337239398</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684036988549336</v>
+        <v>4.684405843773061</v>
       </c>
       <c r="K8" t="n">
-        <v>12.33771463246065</v>
+        <v>12.43491979142257</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76522772313714</v>
+        <v>44.77534457271133</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81028588753951</v>
+        <v>99.810044489696</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.55519586767814</v>
+        <v>85.60079203453058</v>
       </c>
       <c r="C9" t="n">
-        <v>41.48506936066145</v>
+        <v>41.52130683463167</v>
       </c>
       <c r="D9" t="n">
-        <v>1.879824949993404</v>
+        <v>1.88031559160141</v>
       </c>
       <c r="E9" t="n">
-        <v>9.866854148152351</v>
+        <v>9.892994355820919</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508363772201488</v>
+        <v>0.7508965404245185</v>
       </c>
       <c r="G9" t="n">
-        <v>29.0645218009618</v>
+        <v>29.07419293546895</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53847335212684</v>
+        <v>34.54124085952783</v>
       </c>
       <c r="I9" t="n">
-        <v>4.761957881597662</v>
+        <v>4.768048374033713</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69272735762593</v>
+        <v>4.69310337765324</v>
       </c>
       <c r="K9" t="n">
-        <v>14.44480413232186</v>
+        <v>14.3992079654694</v>
       </c>
       <c r="L9" t="n">
-        <v>43.911688530154</v>
+        <v>43.92084480164228</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8415620231373</v>
+        <v>99.84135960174336</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.26662294510572</v>
+        <v>83.48389528682709</v>
       </c>
       <c r="C10" t="n">
-        <v>39.93484739286608</v>
+        <v>40.14373161645031</v>
       </c>
       <c r="D10" t="n">
-        <v>1.777233155021801</v>
+        <v>1.785702377613186</v>
       </c>
       <c r="E10" t="n">
-        <v>9.990804132710002</v>
+        <v>10.05848255308944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520310469731919</v>
+        <v>0.7520897180444285</v>
       </c>
       <c r="G10" t="n">
-        <v>27.47832013810887</v>
+        <v>27.61124551854323</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59342816076683</v>
+        <v>34.5961270300437</v>
       </c>
       <c r="I10" t="n">
-        <v>3.974612267942595</v>
+        <v>3.979687351715446</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700194043582449</v>
+        <v>4.700560737777677</v>
       </c>
       <c r="K10" t="n">
-        <v>16.73337705489426</v>
+        <v>16.5161047131729</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19949894441748</v>
+        <v>43.20771788220917</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86772339217784</v>
+        <v>99.86755421183238</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.98811324017242</v>
+        <v>81.21999596056575</v>
       </c>
       <c r="C11" t="n">
-        <v>38.27190824953925</v>
+        <v>38.49635519543386</v>
       </c>
       <c r="D11" t="n">
-        <v>1.676338301777097</v>
+        <v>1.685535333826597</v>
       </c>
       <c r="E11" t="n">
-        <v>9.976401777424176</v>
+        <v>10.04775054682554</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530576421195824</v>
+        <v>0.7531147671094227</v>
       </c>
       <c r="G11" t="n">
-        <v>25.91835538620693</v>
+        <v>26.06242256040004</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64065153750079</v>
+        <v>34.64327928703343</v>
       </c>
       <c r="I11" t="n">
-        <v>3.316698331896478</v>
+        <v>3.320926170936831</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70661026324739</v>
+        <v>4.706967294433891</v>
       </c>
       <c r="K11" t="n">
-        <v>19.01188675982757</v>
+        <v>18.78000403943425</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60579909430144</v>
+        <v>42.61309389425092</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88959410366826</v>
+        <v>99.88945312911902</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.5672247587607</v>
+        <v>78.80261315893021</v>
       </c>
       <c r="C12" t="n">
-        <v>36.36391717221279</v>
+        <v>36.59268015248949</v>
       </c>
       <c r="D12" t="n">
-        <v>1.570164895787899</v>
+        <v>1.579578950824327</v>
       </c>
       <c r="E12" t="n">
-        <v>9.805724732246413</v>
+        <v>9.877907612434571</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539417389748135</v>
+        <v>0.7539974118867333</v>
       </c>
       <c r="G12" t="n">
-        <v>24.2767773908376</v>
+        <v>24.42408252008331</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68131999284142</v>
+        <v>34.68388094678971</v>
       </c>
       <c r="I12" t="n">
-        <v>2.767160139479966</v>
+        <v>2.770681892619471</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712135868592584</v>
+        <v>4.712483824292082</v>
       </c>
       <c r="K12" t="n">
-        <v>21.4327752412393</v>
+        <v>21.19738684106981</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11117707732858</v>
+        <v>42.11768505724801</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90786949078067</v>
+        <v>99.90775205080732</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.04703390660819</v>
+        <v>76.36873118212796</v>
       </c>
       <c r="C13" t="n">
-        <v>34.2707457028442</v>
+        <v>34.58650144795719</v>
       </c>
       <c r="D13" t="n">
-        <v>1.460650547233986</v>
+        <v>1.47391996022076</v>
       </c>
       <c r="E13" t="n">
-        <v>9.506521144504745</v>
+        <v>9.602373536860842</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547045667374044</v>
+        <v>0.7547580469520817</v>
       </c>
       <c r="G13" t="n">
-        <v>22.58354410809257</v>
+        <v>22.7903408801713</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71641006992061</v>
+        <v>34.71887015979574</v>
       </c>
       <c r="I13" t="n">
-        <v>2.308299928010098</v>
+        <v>2.311230804676723</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716903542108778</v>
+        <v>4.71723779345051</v>
       </c>
       <c r="K13" t="n">
-        <v>23.95296609339182</v>
+        <v>23.63126881787204</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69942264433398</v>
+        <v>41.70526634826469</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92313444057</v>
+        <v>99.92303661409392</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.91498831468924</v>
+        <v>83.17877410534329</v>
       </c>
       <c r="C14" t="n">
-        <v>38.58490830116622</v>
+        <v>38.8081706899854</v>
       </c>
       <c r="D14" t="n">
-        <v>1.462356691350312</v>
+        <v>1.475688540658654</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90199534520936</v>
+        <v>11.95931550123081</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555861155503917</v>
+        <v>0.755663693359762</v>
       </c>
       <c r="G14" t="n">
-        <v>24.51004007656324</v>
+        <v>24.66406950744265</v>
       </c>
       <c r="H14" t="n">
-        <v>36.65707809201091</v>
+        <v>36.60691202259287</v>
       </c>
       <c r="I14" t="n">
-        <v>2.905518771815085</v>
+        <v>2.994226756560058</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722413222189949</v>
+        <v>4.722898083498512</v>
       </c>
       <c r="K14" t="n">
-        <v>17.08501168531075</v>
+        <v>16.82122589465668</v>
       </c>
       <c r="L14" t="n">
-        <v>44.23334238425304</v>
+        <v>44.27091547398172</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90326237073</v>
+        <v>99.90031205862381</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.16886987693873</v>
+        <v>82.42034455138155</v>
       </c>
       <c r="C15" t="n">
-        <v>38.28740406478597</v>
+        <v>38.5121725160301</v>
       </c>
       <c r="D15" t="n">
-        <v>1.434957999150917</v>
+        <v>1.44777333965325</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08294078322897</v>
+        <v>12.14936927795582</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563290057468443</v>
+        <v>0.7564270276965702</v>
       </c>
       <c r="G15" t="n">
-        <v>24.05082034732434</v>
+        <v>24.19750597527333</v>
       </c>
       <c r="H15" t="n">
-        <v>36.6931192306511</v>
+        <v>36.64389052659789</v>
       </c>
       <c r="I15" t="n">
-        <v>2.423646224918772</v>
+        <v>2.497709481101105</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727056285917777</v>
+        <v>4.727668923103563</v>
       </c>
       <c r="K15" t="n">
-        <v>17.83113012306129</v>
+        <v>17.57965544861847</v>
       </c>
       <c r="L15" t="n">
-        <v>43.8007569573801</v>
+        <v>43.82499906989143</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91929114522736</v>
+        <v>99.91682703453999</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.66594337486964</v>
+        <v>79.92596907181643</v>
       </c>
       <c r="C16" t="n">
-        <v>36.15873916462072</v>
+        <v>36.40360423561126</v>
       </c>
       <c r="D16" t="n">
-        <v>1.340490149021238</v>
+        <v>1.353397866862567</v>
       </c>
       <c r="E16" t="n">
-        <v>11.62438458998469</v>
+        <v>11.70459826387757</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569686992569552</v>
+        <v>0.757084224901993</v>
       </c>
       <c r="G16" t="n">
-        <v>22.46747833075572</v>
+        <v>22.62015197639479</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72415380695218</v>
+        <v>36.67572738801099</v>
       </c>
       <c r="I16" t="n">
-        <v>2.021413428542886</v>
+        <v>2.083232946131066</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73105437035597</v>
+        <v>4.731776405637455</v>
       </c>
       <c r="K16" t="n">
-        <v>20.33405662513036</v>
+        <v>20.07403092818355</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43988070400118</v>
+        <v>43.45298401728571</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93267649375227</v>
+        <v>99.93061918108054</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.48420884547403</v>
+        <v>81.67731861889936</v>
       </c>
       <c r="C17" t="n">
-        <v>37.48572354093771</v>
+        <v>37.67066605029657</v>
       </c>
       <c r="D17" t="n">
-        <v>1.341584928238218</v>
+        <v>1.354550863762904</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4489790269006</v>
+        <v>12.50677073302612</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575869161087954</v>
+        <v>0.7577292057948838</v>
       </c>
       <c r="G17" t="n">
-        <v>22.968187285617</v>
+        <v>23.08370792515296</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23650619837728</v>
+        <v>37.15125766839686</v>
       </c>
       <c r="I17" t="n">
-        <v>1.996446264552155</v>
+        <v>2.087494686547629</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734918225679971</v>
+        <v>4.735807536218023</v>
       </c>
       <c r="K17" t="n">
-        <v>18.51579115452597</v>
+        <v>18.32268138110063</v>
       </c>
       <c r="L17" t="n">
-        <v>43.93199140133391</v>
+        <v>43.93712864173175</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9335060967976</v>
+        <v>99.93047607312894</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.1092237042224</v>
+        <v>79.35120487836512</v>
       </c>
       <c r="C18" t="n">
-        <v>35.418637219023</v>
+        <v>35.6665748047787</v>
       </c>
       <c r="D18" t="n">
-        <v>1.255785370652596</v>
+        <v>1.270194532311993</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9302972729752</v>
+        <v>12.01803794606479</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581183693029481</v>
+        <v>0.758283322006622</v>
       </c>
       <c r="G18" t="n">
-        <v>21.49928265932731</v>
+        <v>21.64614144541163</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26262790103269</v>
+        <v>37.17842583613157</v>
       </c>
       <c r="I18" t="n">
-        <v>1.664872322788247</v>
+        <v>1.740851033897151</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738239808143425</v>
+        <v>4.739270762541387</v>
       </c>
       <c r="K18" t="n">
-        <v>20.8907762957776</v>
+        <v>20.64879512163485</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63512964451738</v>
+        <v>43.62664411007124</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94454315931797</v>
+        <v>99.94201403648479</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.21090491988248</v>
+        <v>78.4630275478101</v>
       </c>
       <c r="C19" t="n">
-        <v>34.77639715497206</v>
+        <v>35.04626478105904</v>
       </c>
       <c r="D19" t="n">
-        <v>1.223985442519348</v>
+        <v>1.238664287454127</v>
       </c>
       <c r="E19" t="n">
-        <v>11.85955851750312</v>
+        <v>11.96164621158355</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585669132681322</v>
+        <v>0.7587509422361546</v>
       </c>
       <c r="G19" t="n">
-        <v>20.95486188531583</v>
+        <v>21.10881576604537</v>
       </c>
       <c r="H19" t="n">
-        <v>37.28467449368718</v>
+        <v>37.20135312929311</v>
       </c>
       <c r="I19" t="n">
-        <v>1.388214459663046</v>
+        <v>1.451603822221821</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741043207925826</v>
+        <v>4.742193388975966</v>
       </c>
       <c r="K19" t="n">
-        <v>21.78909508011752</v>
+        <v>21.53697245218989</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38826131149965</v>
+        <v>43.36840579358724</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95375354658923</v>
+        <v>99.95164302683617</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.6559654244424</v>
+        <v>75.96432256086931</v>
       </c>
       <c r="C20" t="n">
-        <v>32.43484082700844</v>
+        <v>32.77078386235364</v>
       </c>
       <c r="D20" t="n">
-        <v>1.132689819813176</v>
+        <v>1.149063332661943</v>
       </c>
       <c r="E20" t="n">
-        <v>11.16787399834995</v>
+        <v>11.29809825855095</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758953748655206</v>
+        <v>0.7591539057861418</v>
       </c>
       <c r="G20" t="n">
-        <v>19.39186358641122</v>
+        <v>19.58187253669194</v>
       </c>
       <c r="H20" t="n">
-        <v>37.3036880193728</v>
+        <v>37.22111032297399</v>
       </c>
       <c r="I20" t="n">
-        <v>1.157435322745017</v>
+        <v>1.210312293040952</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743460929095038</v>
+        <v>4.744711911163385</v>
       </c>
       <c r="K20" t="n">
-        <v>24.34403457555759</v>
+        <v>24.0356774391307</v>
       </c>
       <c r="L20" t="n">
-        <v>43.18256308466555</v>
+        <v>43.15321637012059</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96143848723158</v>
+        <v>99.95967767160494</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.57435291967796</v>
+        <v>81.80240309389748</v>
       </c>
       <c r="C21" t="n">
-        <v>36.14509807173101</v>
+        <v>36.36780296692158</v>
       </c>
       <c r="D21" t="n">
-        <v>1.133438295619097</v>
+        <v>1.14989144445053</v>
       </c>
       <c r="E21" t="n">
-        <v>13.15809234605807</v>
+        <v>13.24472222060133</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594552615219639</v>
+        <v>0.7597010160113696</v>
       </c>
       <c r="G21" t="n">
-        <v>21.11799666977496</v>
+        <v>21.23969798684338</v>
       </c>
       <c r="H21" t="n">
-        <v>39.04165714733893</v>
+        <v>38.8916480930971</v>
       </c>
       <c r="I21" t="n">
-        <v>1.617117814852668</v>
+        <v>1.768610982822702</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746595384512275</v>
+        <v>4.748131350071059</v>
       </c>
       <c r="K21" t="n">
-        <v>18.42564708032203</v>
+        <v>18.19759690610254</v>
       </c>
       <c r="L21" t="n">
-        <v>45.37538651671086</v>
+        <v>45.37568888395052</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94613166876391</v>
+        <v>99.94108875697462</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_98_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.64127654286858</v>
+        <v>45.58676566513314</v>
       </c>
       <c r="M2" t="n">
-        <v>99.03310677052588</v>
+        <v>98.01659902620327</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04731160931718</v>
+        <v>88.04875477844242</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95694574902397</v>
+        <v>45.93976066452268</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228760485392507</v>
+        <v>2.228777217438767</v>
       </c>
       <c r="E3" t="n">
-        <v>5.72350551327634</v>
+        <v>5.713839181346867</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429201617975025</v>
+        <v>0.7429257391462556</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98274080401357</v>
+        <v>33.97674617193385</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17432744268511</v>
+        <v>34.17458400072776</v>
       </c>
       <c r="I3" t="n">
-        <v>6.55180619091776</v>
+        <v>6.568596598184826</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643251011234391</v>
+        <v>4.643285869664097</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95268839068282</v>
+        <v>11.95124522155758</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85519276802567</v>
+        <v>48.87322011024491</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648269077325</v>
+        <v>106.7642259963252</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08078589422487</v>
+        <v>87.13403431390097</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62137433145953</v>
+        <v>42.65987292840551</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181951778964969</v>
+        <v>2.184718031697513</v>
       </c>
       <c r="E4" t="n">
-        <v>6.515178599389378</v>
+        <v>6.515105651772319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444760806760586</v>
+        <v>0.7444847101975505</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26903103200185</v>
+        <v>33.30508291247494</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24589971109869</v>
+        <v>34.24629666908731</v>
       </c>
       <c r="I4" t="n">
-        <v>5.471273187868574</v>
+        <v>5.485316899936636</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652975504225366</v>
+        <v>4.65302943873469</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91921410577512</v>
+        <v>12.86596568609903</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27741694635097</v>
+        <v>44.29170036887921</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81800538358561</v>
+        <v>99.81753898338374</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.80722986251979</v>
+        <v>85.93744693890559</v>
       </c>
       <c r="C5" t="n">
-        <v>42.19698051319777</v>
+        <v>42.31465350058259</v>
       </c>
       <c r="D5" t="n">
-        <v>2.119489615681723</v>
+        <v>2.126252216921773</v>
       </c>
       <c r="E5" t="n">
-        <v>7.089917642335306</v>
+        <v>7.10395594608843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457970193668998</v>
+        <v>0.7458070505755862</v>
       </c>
       <c r="G5" t="n">
-        <v>32.3166471761212</v>
+        <v>32.41379681495578</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30666289087738</v>
+        <v>34.30712432647696</v>
       </c>
       <c r="I5" t="n">
-        <v>4.567484147094148</v>
+        <v>4.579216517789654</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661231371043123</v>
+        <v>4.661294066097413</v>
       </c>
       <c r="K5" t="n">
-        <v>14.19277013748023</v>
+        <v>14.06255306109441</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45826953854787</v>
+        <v>43.47042352443587</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84802018922586</v>
+        <v>99.84763008611287</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.33034745541606</v>
+        <v>84.53809008764317</v>
       </c>
       <c r="C6" t="n">
-        <v>41.42934184460893</v>
+        <v>41.62645747141659</v>
       </c>
       <c r="D6" t="n">
-        <v>2.047189530600626</v>
+        <v>2.05790052853366</v>
       </c>
       <c r="E6" t="n">
-        <v>7.483394833479589</v>
+        <v>7.512548919060425</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469207576779221</v>
+        <v>0.7469309221453226</v>
       </c>
       <c r="G6" t="n">
-        <v>31.21426086430252</v>
+        <v>31.37180484347698</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35835485318441</v>
+        <v>34.35882241868484</v>
       </c>
       <c r="I6" t="n">
-        <v>3.811971880683982</v>
+        <v>3.821764192333676</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668254735487013</v>
+        <v>4.668318263408266</v>
       </c>
       <c r="K6" t="n">
-        <v>15.66965254458394</v>
+        <v>15.46190991235683</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77413105116563</v>
+        <v>42.78443215739908</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87312544035851</v>
+        <v>99.87279954117251</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.63995388027118</v>
+        <v>82.95815881006159</v>
       </c>
       <c r="C7" t="n">
-        <v>40.33081294989967</v>
+        <v>40.64005451790338</v>
       </c>
       <c r="D7" t="n">
-        <v>1.964774668788305</v>
+        <v>1.981022751343799</v>
       </c>
       <c r="E7" t="n">
-        <v>7.712251384697774</v>
+        <v>7.763380464456921</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478790289682603</v>
+        <v>0.7478879814188237</v>
       </c>
       <c r="G7" t="n">
-        <v>29.95765078631405</v>
+        <v>30.19983633024707</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40243533253997</v>
+        <v>34.40284714526589</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180718747911204</v>
+        <v>3.188884253461431</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674243931051627</v>
+        <v>4.674299883867648</v>
       </c>
       <c r="K7" t="n">
-        <v>17.36004611972881</v>
+        <v>17.04184118993841</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20325282257474</v>
+        <v>42.2119441757045</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89411189220323</v>
+        <v>99.89383988354629</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.56508020857744</v>
+        <v>87.84607822085778</v>
       </c>
       <c r="C8" t="n">
-        <v>42.5997801255621</v>
+        <v>42.96173081890865</v>
       </c>
       <c r="D8" t="n">
-        <v>1.969046133648937</v>
+        <v>1.985256248880563</v>
       </c>
       <c r="E8" t="n">
-        <v>9.527661826504991</v>
+        <v>9.609155626339158</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495049350036899</v>
+        <v>0.7494862376351971</v>
       </c>
       <c r="G8" t="n">
-        <v>30.44618012223764</v>
+        <v>30.70964305072222</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47722701016972</v>
+        <v>34.47636693121906</v>
       </c>
       <c r="I8" t="n">
-        <v>5.711054337239398</v>
+        <v>5.631881140841595</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684405843773061</v>
+        <v>4.684288985219982</v>
       </c>
       <c r="K8" t="n">
-        <v>12.43491979142257</v>
+        <v>12.15392177914224</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77534457271133</v>
+        <v>44.69701835766473</v>
       </c>
       <c r="M8" t="n">
-        <v>99.810044489696</v>
+        <v>99.81267095571562</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.60079203453058</v>
+        <v>85.83822804115236</v>
       </c>
       <c r="C9" t="n">
-        <v>41.52130683463167</v>
+        <v>41.82789669787749</v>
       </c>
       <c r="D9" t="n">
-        <v>1.88031559160141</v>
+        <v>1.89448402560839</v>
       </c>
       <c r="E9" t="n">
-        <v>9.892994355820919</v>
+        <v>9.9534283964664</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508965404245185</v>
+        <v>0.7508546787914079</v>
       </c>
       <c r="G9" t="n">
-        <v>29.07419293546895</v>
+        <v>29.30550059949923</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54124085952783</v>
+        <v>34.53931522440476</v>
       </c>
       <c r="I9" t="n">
-        <v>4.768048374033713</v>
+        <v>4.701803373935869</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69310337765324</v>
+        <v>4.6928417424463</v>
       </c>
       <c r="K9" t="n">
-        <v>14.3992079654694</v>
+        <v>14.16177195884766</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92084480164228</v>
+        <v>43.8538902004737</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84135960174336</v>
+        <v>99.84355885719884</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.48389528682709</v>
+        <v>83.60717623856449</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14373161645031</v>
+        <v>40.32624414415756</v>
       </c>
       <c r="D10" t="n">
-        <v>1.785702377613186</v>
+        <v>1.794581657040699</v>
       </c>
       <c r="E10" t="n">
-        <v>10.05848255308944</v>
+        <v>10.0826013672299</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520897180444285</v>
+        <v>0.752029449893565</v>
       </c>
       <c r="G10" t="n">
-        <v>27.61124551854323</v>
+        <v>27.76012524537784</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5961270300437</v>
+        <v>34.59335469510398</v>
       </c>
       <c r="I10" t="n">
-        <v>3.979687351715446</v>
+        <v>3.924299762083737</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700560737777677</v>
+        <v>4.700184061834781</v>
       </c>
       <c r="K10" t="n">
-        <v>16.5161047131729</v>
+        <v>16.3928237614355</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20771788220917</v>
+        <v>43.15032644513095</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86755421183238</v>
+        <v>99.86939435072401</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.21999596056575</v>
+        <v>81.17932811352483</v>
       </c>
       <c r="C11" t="n">
-        <v>38.49635519543386</v>
+        <v>38.50653122812508</v>
       </c>
       <c r="D11" t="n">
-        <v>1.685535333826597</v>
+        <v>1.686925897670845</v>
       </c>
       <c r="E11" t="n">
-        <v>10.04775054682554</v>
+        <v>10.02352732535587</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7531147671094227</v>
+        <v>0.7530406395890793</v>
       </c>
       <c r="G11" t="n">
-        <v>26.06242256040004</v>
+        <v>26.09481380537263</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64327928703343</v>
+        <v>34.63986942109764</v>
       </c>
       <c r="I11" t="n">
-        <v>3.320926170936831</v>
+        <v>3.274647027007003</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706967294433891</v>
+        <v>4.706503997431746</v>
       </c>
       <c r="K11" t="n">
-        <v>18.78000403943425</v>
+        <v>18.82067188647517</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61309389425092</v>
+        <v>42.56378855867521</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88945312911902</v>
+        <v>99.89099167327547</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.80261315893021</v>
+        <v>78.76206066219945</v>
       </c>
       <c r="C12" t="n">
-        <v>36.59268015248949</v>
+        <v>36.59585230374734</v>
       </c>
       <c r="D12" t="n">
-        <v>1.579578950824327</v>
+        <v>1.580889686562641</v>
       </c>
       <c r="E12" t="n">
-        <v>9.877907612434571</v>
+        <v>9.84880983056431</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539974118867333</v>
+        <v>0.7539113328743955</v>
       </c>
       <c r="G12" t="n">
-        <v>24.42408252008331</v>
+        <v>24.45455492422307</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68388094678971</v>
+        <v>34.67992131222218</v>
       </c>
       <c r="I12" t="n">
-        <v>2.770681892619471</v>
+        <v>2.732027745287871</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712483824292082</v>
+        <v>4.711945830464972</v>
       </c>
       <c r="K12" t="n">
-        <v>21.19738684106981</v>
+        <v>21.23793933780056</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11768505724801</v>
+        <v>42.07524594103523</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90775205080732</v>
+        <v>99.90903758258312</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.36873118212796</v>
+        <v>76.27754199628693</v>
       </c>
       <c r="C13" t="n">
-        <v>34.58650144795719</v>
+        <v>34.53309540626854</v>
       </c>
       <c r="D13" t="n">
-        <v>1.47391996022076</v>
+        <v>1.472899012600015</v>
       </c>
       <c r="E13" t="n">
-        <v>9.602373536860842</v>
+        <v>9.555863204004568</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547580469520817</v>
+        <v>0.7546621574649317</v>
       </c>
       <c r="G13" t="n">
-        <v>22.7903408801713</v>
+        <v>22.78406273860767</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71887015979574</v>
+        <v>34.71445924338686</v>
       </c>
       <c r="I13" t="n">
-        <v>2.311230804676723</v>
+        <v>2.278957156067067</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71723779345051</v>
+        <v>4.716638484155824</v>
       </c>
       <c r="K13" t="n">
-        <v>23.63126881787204</v>
+        <v>23.72245800371309</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70526634826469</v>
+        <v>41.66855693042704</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92303661409392</v>
+        <v>99.92411034040867</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.17877410534329</v>
+        <v>83.25763789842546</v>
       </c>
       <c r="C14" t="n">
-        <v>38.8081706899854</v>
+        <v>38.93452862758659</v>
       </c>
       <c r="D14" t="n">
-        <v>1.475688540658654</v>
+        <v>1.47458218033882</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95931550123081</v>
+        <v>11.99065765673014</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755663693359762</v>
+        <v>0.7555245539946841</v>
       </c>
       <c r="G14" t="n">
-        <v>24.66406950744265</v>
+        <v>24.75825699668567</v>
       </c>
       <c r="H14" t="n">
-        <v>36.60691202259287</v>
+        <v>36.70228706244644</v>
       </c>
       <c r="I14" t="n">
-        <v>2.994226756560058</v>
+        <v>2.854300985762925</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722898083498512</v>
+        <v>4.722028462466776</v>
       </c>
       <c r="K14" t="n">
-        <v>16.82122589465668</v>
+        <v>16.74236210157454</v>
       </c>
       <c r="L14" t="n">
-        <v>44.27091547398172</v>
+        <v>44.2280745064234</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90031205862381</v>
+        <v>99.90496523558454</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.42034455138155</v>
+        <v>82.41501366134746</v>
       </c>
       <c r="C15" t="n">
-        <v>38.5121725160301</v>
+        <v>38.50086541038047</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44777333965325</v>
+        <v>1.439761478730603</v>
       </c>
       <c r="E15" t="n">
-        <v>12.14936927795582</v>
+        <v>12.13631658492458</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564270276965702</v>
+        <v>0.7562520950783111</v>
       </c>
       <c r="G15" t="n">
-        <v>24.19750597527333</v>
+        <v>24.2056101040699</v>
       </c>
       <c r="H15" t="n">
-        <v>36.64389052659789</v>
+        <v>36.7696231644553</v>
       </c>
       <c r="I15" t="n">
-        <v>2.497709481101105</v>
+        <v>2.380874639849328</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727668923103563</v>
+        <v>4.726575594239445</v>
       </c>
       <c r="K15" t="n">
-        <v>17.57965544861847</v>
+        <v>17.58498633865253</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82499906989143</v>
+        <v>43.83486211247358</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91682703453999</v>
+        <v>99.92071386150658</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.92596907181643</v>
+        <v>79.83413639156123</v>
       </c>
       <c r="C16" t="n">
-        <v>36.40360423561126</v>
+        <v>36.28774002632952</v>
       </c>
       <c r="D16" t="n">
-        <v>1.353397866862567</v>
+        <v>1.342523145050835</v>
       </c>
       <c r="E16" t="n">
-        <v>11.70459826387757</v>
+        <v>11.6476075675839</v>
       </c>
       <c r="F16" t="n">
-        <v>0.757084224901993</v>
+        <v>0.7568791013869793</v>
       </c>
       <c r="G16" t="n">
-        <v>22.62015197639479</v>
+        <v>22.57081626703995</v>
       </c>
       <c r="H16" t="n">
-        <v>36.67572738801099</v>
+        <v>36.80010874702955</v>
       </c>
       <c r="I16" t="n">
-        <v>2.083232946131066</v>
+        <v>1.985707179801381</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731776405637455</v>
+        <v>4.730494383668621</v>
       </c>
       <c r="K16" t="n">
-        <v>20.07403092818355</v>
+        <v>20.1658636084388</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45298401728571</v>
+        <v>43.48026095856918</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93061918108054</v>
+        <v>99.93386459333749</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.67731861889936</v>
+        <v>81.67582636238892</v>
       </c>
       <c r="C17" t="n">
-        <v>37.67066605029657</v>
+        <v>37.62750161558841</v>
       </c>
       <c r="D17" t="n">
-        <v>1.354550863762904</v>
+        <v>1.343598413400316</v>
       </c>
       <c r="E17" t="n">
-        <v>12.50677073302612</v>
+        <v>12.47584048893532</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577292057948838</v>
+        <v>0.7574853092911823</v>
       </c>
       <c r="G17" t="n">
-        <v>23.08370792515296</v>
+        <v>23.08071443489953</v>
       </c>
       <c r="H17" t="n">
-        <v>37.15125766839686</v>
+        <v>37.32140359575504</v>
       </c>
       <c r="I17" t="n">
-        <v>2.087494686547629</v>
+        <v>1.962500937037632</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735807536218023</v>
+        <v>4.734283183069889</v>
       </c>
       <c r="K17" t="n">
-        <v>18.32268138110063</v>
+        <v>18.32417363761108</v>
       </c>
       <c r="L17" t="n">
-        <v>43.93712864173175</v>
+        <v>43.98296040122722</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93047607312894</v>
+        <v>99.93463565442671</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.35120487836512</v>
+        <v>79.15688755526359</v>
       </c>
       <c r="C18" t="n">
-        <v>35.6665748047787</v>
+        <v>35.41126941398958</v>
       </c>
       <c r="D18" t="n">
-        <v>1.270194532311993</v>
+        <v>1.252742235027907</v>
       </c>
       <c r="E18" t="n">
-        <v>12.01803794606479</v>
+        <v>11.90496250372994</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758283322006622</v>
+        <v>0.758007335215333</v>
       </c>
       <c r="G18" t="n">
-        <v>21.64614144541163</v>
+        <v>21.51996124648752</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17842583613157</v>
+        <v>37.34712388361238</v>
       </c>
       <c r="I18" t="n">
-        <v>1.740851033897151</v>
+        <v>1.636544506094672</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739270762541387</v>
+        <v>4.737545845095831</v>
       </c>
       <c r="K18" t="n">
-        <v>20.64879512163485</v>
+        <v>20.84311244473642</v>
       </c>
       <c r="L18" t="n">
-        <v>43.62664411007124</v>
+        <v>43.69110422635629</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94201403648479</v>
+        <v>99.94548608508229</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.4630275478101</v>
+        <v>78.10865589648516</v>
       </c>
       <c r="C19" t="n">
-        <v>35.04626478105904</v>
+        <v>34.61243676596915</v>
       </c>
       <c r="D19" t="n">
-        <v>1.238664287454127</v>
+        <v>1.215486267572862</v>
       </c>
       <c r="E19" t="n">
-        <v>11.96164621158355</v>
+        <v>11.77871929626686</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587509422361546</v>
+        <v>0.7584494763006255</v>
       </c>
       <c r="G19" t="n">
-        <v>21.10881576604537</v>
+        <v>20.87997095045151</v>
       </c>
       <c r="H19" t="n">
-        <v>37.20135312929311</v>
+        <v>37.36891150906046</v>
       </c>
       <c r="I19" t="n">
-        <v>1.451603822221821</v>
+        <v>1.366809169953945</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742193388975966</v>
+        <v>4.74030922687891</v>
       </c>
       <c r="K19" t="n">
-        <v>21.53697245218989</v>
+        <v>21.89134410351482</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36840579358724</v>
+        <v>43.45068538440908</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95164302683617</v>
+        <v>99.95446625389306</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.96432256086931</v>
+        <v>75.43733021070663</v>
       </c>
       <c r="C20" t="n">
-        <v>32.77078386235364</v>
+        <v>32.15113491175138</v>
       </c>
       <c r="D20" t="n">
-        <v>1.149063332661943</v>
+        <v>1.120196513641945</v>
       </c>
       <c r="E20" t="n">
-        <v>11.29809825855095</v>
+        <v>11.04524024281887</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591539057861418</v>
+        <v>0.7588313892291562</v>
       </c>
       <c r="G20" t="n">
-        <v>19.58187253669194</v>
+        <v>19.2430562875436</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22111032297399</v>
+        <v>37.38772841233006</v>
       </c>
       <c r="I20" t="n">
-        <v>1.210312293040952</v>
+        <v>1.13958118246077</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744711911163385</v>
+        <v>4.742696182682227</v>
       </c>
       <c r="K20" t="n">
-        <v>24.0356774391307</v>
+        <v>24.56266978929335</v>
       </c>
       <c r="L20" t="n">
-        <v>43.15321637012059</v>
+        <v>43.24822837756766</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95967767160494</v>
+        <v>99.96203307861239</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.80240309389748</v>
+        <v>81.7512736734603</v>
       </c>
       <c r="C21" t="n">
-        <v>36.36780296692158</v>
+        <v>36.14136439912962</v>
       </c>
       <c r="D21" t="n">
-        <v>1.14989144445053</v>
+        <v>1.12091453469747</v>
       </c>
       <c r="E21" t="n">
-        <v>13.24472222060133</v>
+        <v>13.17161548609472</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597010160113696</v>
+        <v>0.7593177832755795</v>
       </c>
       <c r="G21" t="n">
-        <v>21.23969798684338</v>
+        <v>21.11268240596908</v>
       </c>
       <c r="H21" t="n">
-        <v>38.8916480930971</v>
+        <v>39.26898486210592</v>
       </c>
       <c r="I21" t="n">
-        <v>1.768610982822702</v>
+        <v>1.572022455845156</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748131350071059</v>
+        <v>4.745736145472373</v>
       </c>
       <c r="K21" t="n">
-        <v>18.19759690610254</v>
+        <v>18.24872632653971</v>
       </c>
       <c r="L21" t="n">
-        <v>45.37568888395052</v>
+        <v>45.55754209200187</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94108875697462</v>
+        <v>99.94763281767119</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_98_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.58676566513314</v>
+        <v>43.47244130723522</v>
       </c>
       <c r="M2" t="n">
-        <v>98.01659902620327</v>
+        <v>96.22782752230222</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04875477844242</v>
+        <v>81.52491760899464</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93976066452268</v>
+        <v>43.2804731645502</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228777217438767</v>
+        <v>2.182377169847563</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713839181346867</v>
+        <v>4.161578903422799</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429257391462556</v>
+        <v>0.7376668494502265</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97674617193385</v>
+        <v>32.82658992979044</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17458400072776</v>
+        <v>33.93267507471042</v>
       </c>
       <c r="I3" t="n">
-        <v>6.568596598184826</v>
+        <v>3.073611872709277</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643285869664097</v>
+        <v>4.610417809063915</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95124522155758</v>
+        <v>18.47508239100535</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87322011024491</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7642259963252</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13403431390097</v>
+        <v>88.71562834680492</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65987292840551</v>
+        <v>42.91170338826805</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184718031697513</v>
+        <v>2.188154171395988</v>
       </c>
       <c r="E4" t="n">
-        <v>6.515105651772319</v>
+        <v>6.571623152737712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444847101975505</v>
+        <v>0.7396195378261744</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30508291247494</v>
+        <v>33.52589870475681</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24629666908731</v>
+        <v>34.02249874000402</v>
       </c>
       <c r="I4" t="n">
-        <v>5.485316899936636</v>
+        <v>7.04521192867062</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65302943873469</v>
+        <v>4.62262211141359</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86596568609903</v>
+        <v>11.28437165319508</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29170036887921</v>
+        <v>45.5697045690284</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81753898338374</v>
+        <v>99.76577961049153</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.93744693890559</v>
+        <v>87.70113674892882</v>
       </c>
       <c r="C5" t="n">
-        <v>42.31465350058259</v>
+        <v>42.98930562560039</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126252216921773</v>
+        <v>2.140433601126063</v>
       </c>
       <c r="E5" t="n">
-        <v>7.10395594608843</v>
+        <v>7.408995291804768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458070505755862</v>
+        <v>0.7412736497825591</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41379681495578</v>
+        <v>32.79474592497711</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30712432647696</v>
+        <v>34.09858788999771</v>
       </c>
       <c r="I5" t="n">
-        <v>4.579216517789654</v>
+        <v>5.884140080099612</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661294066097413</v>
+        <v>4.632960311140994</v>
       </c>
       <c r="K5" t="n">
-        <v>14.06255306109441</v>
+        <v>12.29886325107118</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47042352443587</v>
+        <v>44.51613079197646</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84763008611287</v>
+        <v>99.80429966864803</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.53809008764317</v>
+        <v>86.4724085590905</v>
       </c>
       <c r="C6" t="n">
-        <v>41.62645747141659</v>
+        <v>42.6739619556438</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05790052853366</v>
+        <v>2.082259103454285</v>
       </c>
       <c r="E6" t="n">
-        <v>7.512548919060425</v>
+        <v>8.026416746736233</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469309221453226</v>
+        <v>0.7426774431307399</v>
       </c>
       <c r="G6" t="n">
-        <v>31.37180484347698</v>
+        <v>31.90342284471177</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35882241868484</v>
+        <v>34.16316238401403</v>
       </c>
       <c r="I6" t="n">
-        <v>3.821764192333676</v>
+        <v>4.91273601747632</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668318263408266</v>
+        <v>4.641734019567124</v>
       </c>
       <c r="K6" t="n">
-        <v>15.46190991235683</v>
+        <v>13.52759144090949</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78443215739908</v>
+        <v>43.63499826788838</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87279954117251</v>
+        <v>99.83655166444167</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.95815881006159</v>
+        <v>84.97829270114447</v>
       </c>
       <c r="C7" t="n">
-        <v>40.64005451790338</v>
+        <v>41.94298472695868</v>
       </c>
       <c r="D7" t="n">
-        <v>1.981022751343799</v>
+        <v>2.011435884087292</v>
       </c>
       <c r="E7" t="n">
-        <v>7.763380464456921</v>
+        <v>8.436838716239462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478879814188237</v>
+        <v>0.7438720118680202</v>
       </c>
       <c r="G7" t="n">
-        <v>30.19983633024707</v>
+        <v>30.81830182834035</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40284714526589</v>
+        <v>34.21811254592892</v>
       </c>
       <c r="I7" t="n">
-        <v>3.188884253461431</v>
+        <v>4.100531640505285</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674299883867648</v>
+        <v>4.649200074175126</v>
       </c>
       <c r="K7" t="n">
-        <v>17.04184118993841</v>
+        <v>15.02170729885555</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2119441757045</v>
+        <v>42.89884308481142</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89383988354629</v>
+        <v>99.86353511062565</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.84607822085778</v>
+        <v>83.35342152476917</v>
       </c>
       <c r="C8" t="n">
-        <v>42.96173081890865</v>
+        <v>40.95509554756337</v>
       </c>
       <c r="D8" t="n">
-        <v>1.985256248880563</v>
+        <v>1.93487965037732</v>
       </c>
       <c r="E8" t="n">
-        <v>9.609155626339158</v>
+        <v>8.686026110866532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494862376351971</v>
+        <v>0.744889914715421</v>
       </c>
       <c r="G8" t="n">
-        <v>30.70964305072222</v>
+        <v>29.64534218494338</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47636693121906</v>
+        <v>34.26493607690936</v>
       </c>
       <c r="I8" t="n">
-        <v>5.631881140841595</v>
+        <v>3.421785619985788</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684288985219982</v>
+        <v>4.655561966971381</v>
       </c>
       <c r="K8" t="n">
-        <v>12.15392177914224</v>
+        <v>16.64657847523081</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69701835766473</v>
+        <v>42.28442232052512</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81267095571562</v>
+        <v>99.88609634331931</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.83822804115236</v>
+        <v>81.56552089962869</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82789669787749</v>
+        <v>39.69848523853796</v>
       </c>
       <c r="D9" t="n">
-        <v>1.89448402560839</v>
+        <v>1.851124332051889</v>
       </c>
       <c r="E9" t="n">
-        <v>9.9534283964664</v>
+        <v>8.78583574049992</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508546787914079</v>
+        <v>0.7457589595082437</v>
       </c>
       <c r="G9" t="n">
-        <v>29.30550059949923</v>
+        <v>28.36208145548042</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53931522440476</v>
+        <v>34.3049121373792</v>
       </c>
       <c r="I9" t="n">
-        <v>4.701803373935869</v>
+        <v>2.854814777782495</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6928417424463</v>
+        <v>4.660993496926523</v>
       </c>
       <c r="K9" t="n">
-        <v>14.16177195884766</v>
+        <v>18.43447910037131</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8538902004737</v>
+        <v>41.77198606053556</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84355885719884</v>
+        <v>99.90495039944483</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.60717623856449</v>
+        <v>86.2277977678997</v>
       </c>
       <c r="C10" t="n">
-        <v>40.32624414415756</v>
+        <v>42.94047452116384</v>
       </c>
       <c r="D10" t="n">
-        <v>1.794581657040699</v>
+        <v>1.85317816563778</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0826013672299</v>
+        <v>10.63436915600912</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752029449893565</v>
+        <v>0.7465863835615592</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76012524537784</v>
+        <v>29.75398353083878</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59335469510398</v>
+        <v>35.70340781914122</v>
       </c>
       <c r="I10" t="n">
-        <v>3.924299762083737</v>
+        <v>2.870107815451489</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700184061834781</v>
+        <v>4.666164897259744</v>
       </c>
       <c r="K10" t="n">
-        <v>16.3928237614355</v>
+        <v>13.77220223210032</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15032644513095</v>
+        <v>43.19175901531064</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86939435072401</v>
+        <v>99.9044357685748</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.17932811352483</v>
+        <v>85.99702815253943</v>
       </c>
       <c r="C11" t="n">
-        <v>38.50653122812508</v>
+        <v>43.03849368526075</v>
       </c>
       <c r="D11" t="n">
-        <v>1.686925897670845</v>
+        <v>1.834077249897297</v>
       </c>
       <c r="E11" t="n">
-        <v>10.02352732535587</v>
+        <v>10.99198116482875</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530406395890793</v>
+        <v>0.747295665036519</v>
       </c>
       <c r="G11" t="n">
-        <v>26.09481380537263</v>
+        <v>29.50602758169661</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63986942109764</v>
+        <v>35.79604892884041</v>
       </c>
       <c r="I11" t="n">
-        <v>3.274647027007003</v>
+        <v>2.450999655761618</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706503997431746</v>
+        <v>4.670597906478243</v>
       </c>
       <c r="K11" t="n">
-        <v>18.82067188647517</v>
+        <v>14.00297184746057</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56378855867521</v>
+        <v>42.87691202274435</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89099167327547</v>
+        <v>99.91837755546567</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.76206066219945</v>
+        <v>84.09095516726721</v>
       </c>
       <c r="C12" t="n">
-        <v>36.59585230374734</v>
+        <v>41.51372529504273</v>
       </c>
       <c r="D12" t="n">
-        <v>1.580889686562641</v>
+        <v>1.752914081417114</v>
       </c>
       <c r="E12" t="n">
-        <v>9.84880983056431</v>
+        <v>10.84624698976709</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539113328743955</v>
+        <v>0.7479011950737476</v>
       </c>
       <c r="G12" t="n">
-        <v>24.45455492422307</v>
+        <v>28.20030139817393</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67992131222218</v>
+        <v>35.82505429292138</v>
       </c>
       <c r="I12" t="n">
-        <v>2.732027745287871</v>
+        <v>2.044154740703018</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711945830464972</v>
+        <v>4.674382469210921</v>
       </c>
       <c r="K12" t="n">
-        <v>21.23793933780056</v>
+        <v>15.9090448327328</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07524594103523</v>
+        <v>42.50914654845333</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90903758258312</v>
+        <v>99.93191667622887</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.27754199628693</v>
+        <v>85.22266483333773</v>
       </c>
       <c r="C13" t="n">
-        <v>34.53309540626854</v>
+        <v>42.47604039504921</v>
       </c>
       <c r="D13" t="n">
-        <v>1.472899012600015</v>
+        <v>1.754201720648265</v>
       </c>
       <c r="E13" t="n">
-        <v>9.555863204004568</v>
+        <v>11.47539894922153</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546621574649317</v>
+        <v>0.748450581338603</v>
       </c>
       <c r="G13" t="n">
-        <v>22.78406273860767</v>
+        <v>28.52919079632137</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71445924338686</v>
+        <v>36.15954461073692</v>
       </c>
       <c r="I13" t="n">
-        <v>2.278957156067067</v>
+        <v>1.878062041704774</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716638484155824</v>
+        <v>4.677816133366266</v>
       </c>
       <c r="K13" t="n">
-        <v>23.72245800371309</v>
+        <v>14.77733516666229</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66855693042704</v>
+        <v>42.6840683221184</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92411034040867</v>
+        <v>99.9374438838299</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.25763789842546</v>
+        <v>83.32461272680919</v>
       </c>
       <c r="C14" t="n">
-        <v>38.93452862758659</v>
+        <v>40.87003189123801</v>
       </c>
       <c r="D14" t="n">
-        <v>1.47458218033882</v>
+        <v>1.675517438428548</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99065765673014</v>
+        <v>11.22167814334974</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555245539946841</v>
+        <v>0.7489194694824474</v>
       </c>
       <c r="G14" t="n">
-        <v>24.75825699668567</v>
+        <v>27.24952103332036</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70228706244644</v>
+        <v>36.18219778541208</v>
       </c>
       <c r="I14" t="n">
-        <v>2.854300985762925</v>
+        <v>1.566032172550733</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722028462466776</v>
+        <v>4.680746684265293</v>
       </c>
       <c r="K14" t="n">
-        <v>16.74236210157454</v>
+        <v>16.67538727319081</v>
       </c>
       <c r="L14" t="n">
-        <v>44.2280745064234</v>
+        <v>42.40241244552383</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90496523558454</v>
+        <v>99.94783160995266</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.41501366134746</v>
+        <v>82.45838727492111</v>
       </c>
       <c r="C15" t="n">
-        <v>38.50086541038047</v>
+        <v>40.22400492759346</v>
       </c>
       <c r="D15" t="n">
-        <v>1.439761478730603</v>
+        <v>1.639134688682934</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13631658492458</v>
+        <v>11.19932524391018</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562520950783111</v>
+        <v>0.7493214896103587</v>
       </c>
       <c r="G15" t="n">
-        <v>24.2056101040699</v>
+        <v>26.657815759651</v>
       </c>
       <c r="H15" t="n">
-        <v>36.7696231644553</v>
+        <v>36.20162039675353</v>
       </c>
       <c r="I15" t="n">
-        <v>2.380874639849328</v>
+        <v>1.327910386248342</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726575594239445</v>
+        <v>4.683259310064739</v>
       </c>
       <c r="K15" t="n">
-        <v>17.58498633865253</v>
+        <v>17.5416127250789</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83486211247358</v>
+        <v>42.19014241579056</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92071386150658</v>
+        <v>99.95576006846292</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.83413639156123</v>
+        <v>80.19127657141212</v>
       </c>
       <c r="C16" t="n">
-        <v>36.28774002632952</v>
+        <v>38.16291847643554</v>
       </c>
       <c r="D16" t="n">
-        <v>1.342523145050835</v>
+        <v>1.545758359902136</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6476075675839</v>
+        <v>10.74585191108219</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568791013869793</v>
+        <v>0.7496663212764583</v>
       </c>
       <c r="G16" t="n">
-        <v>22.57081626703995</v>
+        <v>25.13920414942927</v>
       </c>
       <c r="H16" t="n">
-        <v>36.80010874702955</v>
+        <v>36.21828008855472</v>
       </c>
       <c r="I16" t="n">
-        <v>1.985707179801381</v>
+        <v>1.107101233189466</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730494383668621</v>
+        <v>4.685414507977861</v>
       </c>
       <c r="K16" t="n">
-        <v>20.1658636084388</v>
+        <v>19.8087234285879</v>
       </c>
       <c r="L16" t="n">
-        <v>43.48026095856918</v>
+        <v>41.99147169535856</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93386459333749</v>
+        <v>99.96311360038199</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.67582636238892</v>
+        <v>84.8032720315605</v>
       </c>
       <c r="C17" t="n">
-        <v>37.62750161558841</v>
+        <v>41.21887372050472</v>
       </c>
       <c r="D17" t="n">
-        <v>1.343598413400316</v>
+        <v>1.546501575495723</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47584048893532</v>
+        <v>12.37288114133309</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574853092911823</v>
+        <v>0.7500267681059324</v>
       </c>
       <c r="G17" t="n">
-        <v>23.08071443489953</v>
+        <v>26.56928266935229</v>
       </c>
       <c r="H17" t="n">
-        <v>37.32140359575504</v>
+        <v>37.65368553551504</v>
       </c>
       <c r="I17" t="n">
-        <v>1.962500937037632</v>
+        <v>1.223227041096359</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734283183069889</v>
+        <v>4.687667300662074</v>
       </c>
       <c r="K17" t="n">
-        <v>18.32417363761108</v>
+        <v>15.19672796843948</v>
       </c>
       <c r="L17" t="n">
-        <v>43.98296040122722</v>
+        <v>43.54364367157805</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93463565442671</v>
+        <v>99.95924536052226</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.15688755526359</v>
+        <v>86.47272418515517</v>
       </c>
       <c r="C18" t="n">
-        <v>35.41126941398958</v>
+        <v>41.94402140648755</v>
       </c>
       <c r="D18" t="n">
-        <v>1.252742235027907</v>
+        <v>1.547764514335808</v>
       </c>
       <c r="E18" t="n">
-        <v>11.90496250372994</v>
+        <v>12.97128435999692</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758007335215333</v>
+        <v>0.7506392718056072</v>
       </c>
       <c r="G18" t="n">
-        <v>21.51996124648752</v>
+        <v>26.70858652887667</v>
       </c>
       <c r="H18" t="n">
-        <v>37.34712388361238</v>
+        <v>37.6844351336329</v>
       </c>
       <c r="I18" t="n">
-        <v>1.636544506094672</v>
+        <v>2.11851892772223</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737545845095831</v>
+        <v>4.691495448785042</v>
       </c>
       <c r="K18" t="n">
-        <v>20.84311244473642</v>
+        <v>13.52727581484483</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69110422635629</v>
+        <v>44.45814310310341</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94548608508229</v>
+        <v>99.92944032443579</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.10865589648516</v>
+        <v>83.9922895229904</v>
       </c>
       <c r="C19" t="n">
-        <v>34.61243676596915</v>
+        <v>39.79207875281165</v>
       </c>
       <c r="D19" t="n">
-        <v>1.215486267572862</v>
+        <v>1.455664125187011</v>
       </c>
       <c r="E19" t="n">
-        <v>11.77871929626686</v>
+        <v>12.49386757627459</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584494763006255</v>
+        <v>0.7511655629926022</v>
       </c>
       <c r="G19" t="n">
-        <v>20.87997095045151</v>
+        <v>25.11928066862475</v>
       </c>
       <c r="H19" t="n">
-        <v>37.36891150906046</v>
+        <v>37.71085659443658</v>
       </c>
       <c r="I19" t="n">
-        <v>1.366809169953945</v>
+        <v>1.766670226771129</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74030922687891</v>
+        <v>4.69478476870376</v>
       </c>
       <c r="K19" t="n">
-        <v>21.89134410351482</v>
+        <v>16.0077104770096</v>
       </c>
       <c r="L19" t="n">
-        <v>43.45068538440908</v>
+        <v>44.14136302218646</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95446625389306</v>
+        <v>99.9411522520077</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.43733021070663</v>
+        <v>81.33880219299803</v>
       </c>
       <c r="C20" t="n">
-        <v>32.15113491175138</v>
+        <v>37.41186146791591</v>
       </c>
       <c r="D20" t="n">
-        <v>1.120196513641945</v>
+        <v>1.357616983643896</v>
       </c>
       <c r="E20" t="n">
-        <v>11.04524024281887</v>
+        <v>11.89785452890958</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588313892291562</v>
+        <v>0.7516190376155607</v>
       </c>
       <c r="G20" t="n">
-        <v>19.2430562875436</v>
+        <v>23.42735625792907</v>
       </c>
       <c r="H20" t="n">
-        <v>37.38772841233006</v>
+        <v>37.73362243637358</v>
       </c>
       <c r="I20" t="n">
-        <v>1.13958118246077</v>
+        <v>1.4731139634291</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742696182682227</v>
+        <v>4.697618985097251</v>
       </c>
       <c r="K20" t="n">
-        <v>24.56266978929335</v>
+        <v>18.66119780700197</v>
       </c>
       <c r="L20" t="n">
-        <v>43.24822837756766</v>
+        <v>43.87786655211628</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96203307861239</v>
+        <v>99.95092582703415</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.7512736734603</v>
+        <v>78.77925830082505</v>
       </c>
       <c r="C21" t="n">
-        <v>36.14136439912962</v>
+        <v>35.07950207751249</v>
       </c>
       <c r="D21" t="n">
-        <v>1.12091453469747</v>
+        <v>1.263545589809996</v>
       </c>
       <c r="E21" t="n">
-        <v>13.17161548609472</v>
+        <v>11.27813916093004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593177832755795</v>
+        <v>0.7520096494265802</v>
       </c>
       <c r="G21" t="n">
-        <v>21.11268240596908</v>
+        <v>21.80403827975269</v>
       </c>
       <c r="H21" t="n">
-        <v>39.26898486210592</v>
+        <v>37.75323236887736</v>
       </c>
       <c r="I21" t="n">
-        <v>1.572022455845156</v>
+        <v>1.22823294311226</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745736145472373</v>
+        <v>4.700060308916123</v>
       </c>
       <c r="K21" t="n">
-        <v>18.24872632653971</v>
+        <v>21.22074169917495</v>
       </c>
       <c r="L21" t="n">
-        <v>45.55754209200187</v>
+        <v>43.65883639099508</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94763281767119</v>
+        <v>99.95908016768252</v>
       </c>
     </row>
   </sheetData>
